--- a/AAII_Financials/Yearly/NTAP_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/NTAP_YR_FIN.xlsx
@@ -656,226 +656,238 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46136</v>
+      </c>
+      <c r="E7" s="2">
         <v>45772</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45408</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45044</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44680</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44316</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43945</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43581</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43217</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42853</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42489</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42118</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41754</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41390</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>41026</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>6925000</v>
+      </c>
+      <c r="E8" s="3">
         <v>6572000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>6268000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>6362000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>6318000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>5744000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>5412000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>6146000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>5919000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>5491000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>5546000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>6122700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>6325100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>6332400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>6233200</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2026000</v>
+      </c>
+      <c r="E9" s="3">
         <v>1959000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1835000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2153000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2098000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1929000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1789000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2201000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2210000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2127000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2173000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2289500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2406000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2571300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2519800</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>4899000</v>
+      </c>
+      <c r="E10" s="3">
         <v>4613000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>4433000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>4209000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>4220000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>3815000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>3623000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>3945000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>3709000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>3364000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>3373000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>3833200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>3919100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>3761100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>3713400</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -894,56 +906,60 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>991000</v>
+      </c>
+      <c r="E12" s="3">
         <v>1012000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>1029000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>956000</v>
-      </c>
-      <c r="G12" s="3">
-        <v>881000</v>
       </c>
       <c r="H12" s="3">
         <v>881000</v>
       </c>
       <c r="I12" s="3">
+        <v>881000</v>
+      </c>
+      <c r="J12" s="3">
         <v>847000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>827000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>783000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>779000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>861000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>919300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>917300</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>904200</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>828200</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -989,87 +1005,93 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>21000</v>
+      </c>
+      <c r="E14" s="3">
         <v>88000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>54000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>109000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>46000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-90000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-31000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-38000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-218000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>52000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>116000</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>88300</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>1700</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>9800</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>189000</v>
+      </c>
+      <c r="E15" s="3">
         <v>215000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>221000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>206000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>161000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>166000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>154000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>161000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>162000</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1085,9 +1107,12 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1103,104 +1128,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>5230000</v>
+      </c>
+      <c r="E17" s="3">
         <v>5147000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>5000000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>5203000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>5115000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>4811000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>4484000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>4963000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4979000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4870000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5198000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>5406200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>5590800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>5724600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>5486700</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>1695000</v>
+      </c>
+      <c r="E18" s="3">
         <v>1425000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1268000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1159000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1203000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>933000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>928000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1183000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>940000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>621000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>348000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>716500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>734300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>607800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>746500</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1219,248 +1251,264 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>30000</v>
+      </c>
+      <c r="E20" s="3">
         <v>2000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-14000</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-4000</v>
       </c>
       <c r="H20" s="3">
         <v>-4000</v>
       </c>
       <c r="I20" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="J20" s="3">
         <v>8000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-17000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-24000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>52000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>46000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>38300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>42500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>50500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>40600</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>1854000</v>
+      </c>
+      <c r="E21" s="3">
         <v>1638000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1490000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1379000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1368000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1103000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1074000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1361000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1126000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>899000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>673000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1062000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1110900</v>
       </c>
-      <c r="P21" s="3" t="s">
+      <c r="Q21" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1080200</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
-        <v>64000</v>
+        <v>109000</v>
       </c>
       <c r="E22" s="3">
         <v>64000</v>
       </c>
       <c r="F22" s="3">
+        <v>64000</v>
+      </c>
+      <c r="G22" s="3">
         <v>67000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>73000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>74000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>55000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>58000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>62000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>52000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>49000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>42000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>36100</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>91700</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>74700</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>1648000</v>
+      </c>
+      <c r="E23" s="3">
         <v>1383000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1263000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1066000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1095000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>962000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>944000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1268000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1199000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>621000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>345000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>712800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>740700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>566600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>712400</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>372000</v>
+      </c>
+      <c r="E24" s="3">
         <v>197000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>277000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-208000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>158000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>232000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>125000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>99000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1083000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>140000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>116000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>152900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>103200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>61300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>107000</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1506,105 +1554,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>1276000</v>
+      </c>
+      <c r="E26" s="3">
         <v>1186000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>986000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1274000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>937000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>730000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>819000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1169000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>116000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>481000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>229000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>559900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>637500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>505300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>605400</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>1276000</v>
+      </c>
+      <c r="E27" s="3">
         <v>1186000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>986000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1274000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>937000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>730000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>819000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1169000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>116000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>481000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>229000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>559900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>637500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>505300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>605400</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1650,9 +1707,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -1680,8 +1740,8 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>24</v>
+      <c r="L29" s="3">
+        <v>0</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>24</v>
@@ -1698,9 +1758,12 @@
       <c r="Q29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1746,9 +1809,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1794,105 +1860,114 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-30000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-2000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>14000</v>
-      </c>
-      <c r="G32" s="3">
-        <v>4000</v>
       </c>
       <c r="H32" s="3">
         <v>4000</v>
       </c>
       <c r="I32" s="3">
+        <v>4000</v>
+      </c>
+      <c r="J32" s="3">
         <v>-8000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>17000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>24000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-52000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-46000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-38300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-42500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-50500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-40600</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1276000</v>
+      </c>
+      <c r="E33" s="3">
         <v>1186000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>986000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1274000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>937000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>730000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>819000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1169000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>116000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>481000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>229000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>559900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>637500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>505300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>605400</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1938,110 +2013,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1276000</v>
+      </c>
+      <c r="E35" s="3">
         <v>1186000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>986000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1274000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>937000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>730000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>819000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1169000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>116000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>481000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>229000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>559900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>637500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>505300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>605400</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46136</v>
+      </c>
+      <c r="E38" s="2">
         <v>45772</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45408</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45044</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44680</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44316</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43945</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43581</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43217</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42853</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42489</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42118</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41754</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41390</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>41026</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2060,8 +2144,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2080,440 +2165,468 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2070000</v>
+      </c>
+      <c r="E41" s="3">
         <v>2742000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1903000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2316000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>4112000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>4529000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2658000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2325000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2941000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2444000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2868000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1922000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2291000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>3277100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1549800</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>1111000</v>
+        <v>1514000</v>
       </c>
       <c r="E42" s="3">
+        <v>1104000</v>
+      </c>
+      <c r="F42" s="3">
         <v>1355000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>761000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>28000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>75000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>230000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1580000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>2456000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>2477000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>2435000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>3404000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>2712300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>3675500</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>3848700</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1286000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1246000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1007000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>987000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1230000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>945000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>973000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1216000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1047000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>731000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>813000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>779000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1711800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>800900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>830900</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>186000</v>
+        <v>198000</v>
       </c>
       <c r="E44" s="3">
         <v>186000</v>
       </c>
       <c r="F44" s="3">
+        <v>186000</v>
+      </c>
+      <c r="G44" s="3">
         <v>167000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>204000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>114000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>145000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>131000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>122000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>163000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>98000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>146000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>122400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>139500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>161500</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>566000</v>
+        <v>708000</v>
       </c>
       <c r="E45" s="3">
+        <v>573000</v>
+      </c>
+      <c r="F45" s="3">
         <v>446000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>449000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>371000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>338000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>268000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>358000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>386000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>383000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>234000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>522000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>489700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>525200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>435600</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5776000</v>
+      </c>
+      <c r="E46" s="3">
         <v>5851000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>4897000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>4680000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>5945000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>6001000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>4274000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>5610000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>6952000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>6198000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>6448000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>6773000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>6471300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>8418200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>6826500</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>98000</v>
+      </c>
+      <c r="E47" s="3">
         <v>92000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>85000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>80000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>73000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>103000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>94000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>29000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>25000</v>
-      </c>
-      <c r="L47" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="M47" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="N47" s="3">
-        <v>0</v>
+      <c r="N47" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="O47" s="3">
+        <v>0</v>
+      </c>
+      <c r="P47" s="3">
         <v>36000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>42000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>51000</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>820000</v>
+      </c>
+      <c r="E48" s="3">
         <v>804000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>851000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>931000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>896000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>639000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>864000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>759000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>756000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>799000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>937000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1030000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1108800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1170900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1137200</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2794000</v>
+      </c>
+      <c r="E49" s="3">
         <v>2766000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2883000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2940000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2488000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2140000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1822000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1782000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1833000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1815000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1856000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1117000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1109600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1168700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1141200</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2559,9 +2672,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2607,57 +2723,63 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>397000</v>
+      </c>
+      <c r="E52" s="3">
         <v>316000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>275000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>239000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>262000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>147000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>159000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>263000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>125000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>681000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>796000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>481000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>488100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>442600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>376400</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2703,57 +2825,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>10744000</v>
+      </c>
+      <c r="E54" s="3">
         <v>10823000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>9887000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>9818000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>10026000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>9360000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>7522000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>8741000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>9991000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>9493000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>10037000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>9401000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>9213800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>11242400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>9532300</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2772,8 +2900,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2792,296 +2921,315 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>550000</v>
+      </c>
+      <c r="E57" s="3">
         <v>511000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>517000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>392000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>607000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>420000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>426000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>542000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>609000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>347000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>254000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>284000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>247000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>259700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>233100</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>42000</v>
+      </c>
+      <c r="E58" s="3">
         <v>790000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>440000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>47000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>297000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>49000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>573000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>649000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>385000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1249000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>849000</v>
       </c>
-      <c r="N58" s="3" t="s">
+      <c r="O58" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
       <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3">
         <v>1257800</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1202300</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>2297000</v>
+        <v>2349000</v>
       </c>
       <c r="E59" s="3">
+        <v>2425000</v>
+      </c>
+      <c r="F59" s="3">
         <v>2194000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2239000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2188000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2084000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1922000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1850000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1737000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2526000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2559000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2425000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2447600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2313100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2084400</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4021000</v>
+      </c>
+      <c r="E60" s="3">
         <v>4662000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>4106000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3467000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3953000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3452000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3616000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3867000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3531000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>4122000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3662000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2709000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2694600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3830600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>3519800</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2691000</v>
+      </c>
+      <c r="E61" s="3">
         <v>2701000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2212000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2637000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2643000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2703000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1239000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1144000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1541000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>744000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1490000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1487000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>990100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>994600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>62600</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>156000</v>
+      </c>
+      <c r="E62" s="3">
         <v>163000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>365000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>460000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>531000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>579000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>621000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>797000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>992000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1847000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2004000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1791000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1742600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1699700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1656300</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3127,9 +3275,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -3175,9 +3326,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3223,57 +3377,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>9393000</v>
+      </c>
+      <c r="E66" s="3">
         <v>9783000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>8741000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>8659000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>9188000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>8675000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>7280000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>7651000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>7715000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>6713000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>7156000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5987000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>5427300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>6524900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>5238700</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3292,8 +3452,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3339,9 +3500,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3387,9 +3551,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3435,9 +3602,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3483,57 +3653,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3" t="s">
+      <c r="D72" s="3">
+        <v>153000</v>
+      </c>
+      <c r="E72" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>208000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>265000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>122000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>211000</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="J72" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="K72" s="3">
+      <c r="K72" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L72" s="3">
         <v>-9000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>40000</v>
       </c>
-      <c r="M72" s="3">
-        <v>0</v>
-      </c>
       <c r="N72" s="3">
+        <v>0</v>
+      </c>
+      <c r="O72" s="3">
         <v>53000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2896800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>2805300</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3579,9 +3755,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3627,9 +3806,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3675,57 +3857,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1351000</v>
+      </c>
+      <c r="E76" s="3">
         <v>1040000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1146000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1159000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>838000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>685000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>242000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1090000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2276000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2780000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2881000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3414000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3786500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>4717500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>4293600</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3771,110 +3959,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46136</v>
+      </c>
+      <c r="E80" s="2">
         <v>45772</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45408</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45044</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44680</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44316</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43945</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43581</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43217</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42853</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42489</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42118</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41754</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41390</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>41026</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1276000</v>
+      </c>
+      <c r="E81" s="3">
         <v>1186000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>986000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1274000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>937000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>730000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>819000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1169000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>116000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>481000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>229000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>559900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>637500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>505300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>605400</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3893,56 +4090,60 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>179000</v>
+      </c>
+      <c r="E83" s="3">
         <v>196000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>198000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>180000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>148000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>158000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>154000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>151000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>145000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>226000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>279000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>307200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>334100</v>
       </c>
-      <c r="P83" s="3" t="s">
+      <c r="Q83" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>293100</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3988,9 +4189,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4036,9 +4240,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4084,9 +4291,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4132,9 +4342,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4180,57 +4393,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>2067000</v>
+      </c>
+      <c r="E89" s="3">
         <v>1506000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1685000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1107000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1211000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1333000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1060000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1341000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1478000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>986000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>974000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1268100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1349600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1386300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1462600</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4249,56 +4468,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-198000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-168000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-155000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-239000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-226000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-162000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-124000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-173000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-145000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-175000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-160000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-175300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-221400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-303300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-407100</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4344,9 +4567,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4392,57 +4618,63 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-595000</v>
+      </c>
+      <c r="E94" s="3">
         <v>147000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-735000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1390000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-561000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>21000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>1269000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>704000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-21000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-223000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>85000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-903200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>760400</v>
       </c>
-      <c r="P94" s="3" t="s">
+      <c r="Q94" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-2310400</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4461,56 +4693,60 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>413000</v>
+      </c>
+      <c r="E96" s="3">
         <v>424000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>416000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>432000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>446000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>427000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>439000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>403000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>214000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-208000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-210000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-207400</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-202300</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4556,9 +4792,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4604,9 +4843,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4652,151 +4894,163 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2147000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-828000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1344000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1513000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1017000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>444000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1960000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-2631000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-986000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1179000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-109000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-675200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-3104000</v>
       </c>
-      <c r="P100" s="3" t="s">
+      <c r="Q100" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-343600</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E101" s="3">
         <v>15000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-19000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-1000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-49000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>71000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-34000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-30000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>26000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-11000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-4000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-59200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>7900</v>
       </c>
-      <c r="P101" s="3" t="s">
+      <c r="Q101" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-16100</v>
       </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-674000</v>
+      </c>
+      <c r="E102" s="3">
         <v>840000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-413000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1797000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-416000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1869000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>335000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-616000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>497000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-427000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>946000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-369500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-986100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1727300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-1207500</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
